--- a/public/invoices/GS-PHONEBOX-001-V3.1.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V3.1.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
+          <t>Venue: Lincoln Road Mall</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <row r="12" ht="98" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V3.1 proposed update — yellow Miami palette throughout (paint, vinyl, lightbox, signage), operating hours extended to 11 AM–8 PM, back-of-house staff compartment with separate back access door, simplified consumer walkie-talkie pair, basic selfie/belfie mounts (no ring lights), Content Capture &amp; Media Handoff Platform removed, 200-unit custom packaging added, and a local NYC install crew + in-store fixture setup + store wayfinding for the post-Miami delivery. Activation remains Friday, July 17, 2026 at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>V3.1 proposed update — yellow Miami palette throughout (paint, vinyl, lightbox, signage), operating hours extended to 11 AM–8 PM, back-of-house staff compartment with separate back access door, simplified consumer walkie-talkie pair, basic selfie/belfie mounts (no ring lights), Content Capture &amp; Media Handoff Platform removed, 200-unit custom packaging added, and a local NYC install crew + in-store fixture setup + store wayfinding for the post-Miami delivery. Activation remains Friday, July 17, 2026 at Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation, yellow palette</t>
+          <t>Portable A-frame signage, branded stanchions, pavement decals for the Lincoln Road Mall street activation, yellow palette</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
@@ -1016,7 +1016,7 @@
     <row r="38" ht="24" customHeight="1">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM, V3.1)</t>
+          <t>Phase 04a  —  The Activation (Lincoln Road Mall, 11 AM–8 PM, V3.1)</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Complete de-installation, module breakdown, crated outbound freight within Euclid Oval's contracted strike window. Site walk-through with the Lincoln Road BID operations team.</t>
+          <t>Complete de-installation, module breakdown, crated outbound freight within the Lincoln Road BID's contracted strike window. Site walk-through with the BID operations team.</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
@@ -1068,7 +1068,7 @@
     <row r="42" ht="22" customHeight="1">
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Subtotal — The Activation (Euclid Oval)</t>
+          <t>Subtotal — The Activation (Lincoln Road Mall)</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
